--- a/05_Figures/F06_prediction/proteins/acute/comp_hypertrophy/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/acute/comp_hypertrophy/spls/c_data/results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="183">
   <si>
     <t xml:space="preserve">level</t>
   </si>
@@ -140,6 +140,9 @@
     <t xml:space="preserve">AIMP1</t>
   </si>
   <si>
+    <t xml:space="preserve">AKR1C3</t>
+  </si>
+  <si>
     <t xml:space="preserve">ALDH1B1</t>
   </si>
   <si>
@@ -152,9 +155,15 @@
     <t xml:space="preserve">DLST</t>
   </si>
   <si>
+    <t xml:space="preserve">DYSF</t>
+  </si>
+  <si>
     <t xml:space="preserve">EEF1A1</t>
   </si>
   <si>
+    <t xml:space="preserve">GPD1L</t>
+  </si>
+  <si>
     <t xml:space="preserve">LYRM7</t>
   </si>
   <si>
@@ -164,43 +173,43 @@
     <t xml:space="preserve">MLEC</t>
   </si>
   <si>
+    <t xml:space="preserve">OTUB1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PADI2</t>
+  </si>
+  <si>
     <t xml:space="preserve">PBXIP1</t>
   </si>
   <si>
     <t xml:space="preserve">TOM1</t>
   </si>
   <si>
-    <t xml:space="preserve">AKR1C3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DYSF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OTUB1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PADI2</t>
+    <t xml:space="preserve">VARS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APOO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DHRS7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RNF123</t>
   </si>
   <si>
     <t xml:space="preserve">RTN3</t>
   </si>
   <si>
-    <t xml:space="preserve">VARS1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APOO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DHRS7</t>
-  </si>
-  <si>
     <t xml:space="preserve">GATD3B</t>
   </si>
   <si>
-    <t xml:space="preserve">GPD1L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF123</t>
+    <t xml:space="preserve">HADHA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYLK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHKG1</t>
   </si>
   <si>
     <t xml:space="preserve">RTN4</t>
@@ -212,19 +221,13 @@
     <t xml:space="preserve">CAMK2D</t>
   </si>
   <si>
-    <t xml:space="preserve">HADHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MYLK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PHKG1</t>
+    <t xml:space="preserve">COQ3</t>
   </si>
   <si>
     <t xml:space="preserve">TMEM43</t>
   </si>
   <si>
-    <t xml:space="preserve">COQ3</t>
+    <t xml:space="preserve">UBE2M</t>
   </si>
   <si>
     <t xml:space="preserve">EEF2</t>
@@ -233,297 +236,312 @@
     <t xml:space="preserve">EIF3E</t>
   </si>
   <si>
+    <t xml:space="preserve">MRPL47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JPT2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDLIM3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACTR1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDC37</t>
+  </si>
+  <si>
     <t xml:space="preserve">MYO18A</t>
   </si>
   <si>
-    <t xml:space="preserve">UBE2M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDC37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRPL47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACTR1A</t>
+    <t xml:space="preserve">MYPN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAP1LC3B2</t>
   </si>
   <si>
     <t xml:space="preserve">BIN1</t>
   </si>
   <si>
+    <t xml:space="preserve">NAMPT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALDH3A2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BZW2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LDHB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAFAH1B3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMA7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUVBL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALDOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HRC</t>
+  </si>
+  <si>
     <t xml:space="preserve">MTARC2</t>
   </si>
   <si>
-    <t xml:space="preserve">MYPN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NAMPT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDLIM3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAP1LC3B2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL7</t>
+    <t xml:space="preserve">MYLK2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRKCSH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSME3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUCLG2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOLLIP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSFM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUBA8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALDH1L1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP5F1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLIP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DYNC1H1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECI2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENDOD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HINT3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRPS27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEDD8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDLIM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PM20D2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRKACA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMC4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PTPN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QDPR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEPTIN9</t>
   </si>
   <si>
     <t xml:space="preserve">STAT5B</t>
   </si>
   <si>
-    <t xml:space="preserve">BZW2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JPT2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUVBL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALDH3A2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HRC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LDHB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAFAH1B3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRKCSH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMA7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSME3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUCLG2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOLLIP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSFM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUBA8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALDH1L1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALDOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP5F1A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLIP2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COA3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DYNC1H1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ECI2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GPT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HINT3</t>
+    <t xml:space="preserve">TCP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADSS2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AFG3L2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AKR1A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C11orf68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COX19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CPT1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CPT2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRYAB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DARS2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DDX1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DLAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DNAJA4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DUSP3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECI1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FECH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FTL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FUS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSDL2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSP90AA1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSP90AB1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSPA2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSPA4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDH3A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISCU</t>
   </si>
   <si>
     <t xml:space="preserve">LMAN2</t>
   </si>
   <si>
+    <t xml:space="preserve">LSS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAPRE1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAPRE3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME1</t>
+  </si>
+  <si>
     <t xml:space="preserve">ME2</t>
   </si>
   <si>
-    <t xml:space="preserve">MRPS27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MYLK2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NEDD8</t>
+    <t xml:space="preserve">METTL26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEK7</t>
   </si>
   <si>
     <t xml:space="preserve">NNMT</t>
   </si>
   <si>
-    <t xml:space="preserve">PRKACA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMC4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PTPN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL12</t>
+    <t xml:space="preserve">NQO2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NT5C3A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAFAH1B2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAIP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PFKFB1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PGP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHKA1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLIN2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PNPO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPIF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPM1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRKAR1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPS20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPS7</t>
   </si>
   <si>
     <t xml:space="preserve">S100A13</t>
   </si>
   <si>
-    <t xml:space="preserve">TCP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADSS2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AFG3L2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AKR1A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C11orf68</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COX19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CPT1A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CPT2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CRYAB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DARS2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DLAT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DNAJA4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DUSP3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ECI1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF3B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENDOD1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FECH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FTL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FUS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSDL2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSP90AA1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSP90AB1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSPA2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSPA4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ISCU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAPRE1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAPRE3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">METTL26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NQO2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NT5C3A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAFAH1B2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAIP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDLIM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PFKFB1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PGLS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PGP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLIN2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PNPO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPIF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPM1A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRKAR1A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QDPR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPS20</t>
-  </si>
-  <si>
     <t xml:space="preserve">SLC25A6</t>
   </si>
   <si>
@@ -537,6 +555,9 @@
   </si>
   <si>
     <t xml:space="preserve">STT3B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SYNCRIP</t>
   </si>
   <si>
     <t xml:space="preserve">TKFC</t>
@@ -929,16 +950,16 @@
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.438235074784531</v>
+        <v>-0.341308375411348</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0285714285714286</v>
+        <v>-0.00714285714285714</v>
       </c>
       <c r="J2"/>
       <c r="K2"/>
@@ -962,29 +983,21 @@
         <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="G3" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.438235074784531</v>
+        <v>-0.341308375411348</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0285714285714286</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.437810945273632</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.402985074626866</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-0.653400653324416</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.701480703498838</v>
-      </c>
+        <v>-0.00714285714285714</v>
+      </c>
+      <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1008,2206 +1021,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-0.308179550593762</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="n">
-        <v>-0.394044098379096</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="n">
-        <v>-3.69702740238172</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-0.289796202323194</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="n">
-        <v>-0.591134318927029</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="n">
-        <v>-0.377966767212337</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="n">
-        <v>-2.11439435570206</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-1.25456231734368</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-0.835996834124872</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-1.27374993754824</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-0.672098674353409</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" t="n">
-        <v>-0.723858671133303</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-0.157728546274721</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" t="n">
-        <v>-2.07259953912554</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.117518365242167</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="n">
-        <v>-3.09600690597255</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" t="n">
-        <v>-0.608777096806264</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.583636413614922</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" t="n">
-        <v>-0.153079140349234</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" t="n">
-        <v>-0.746727407260529</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" t="n">
-        <v>-0.463390726652066</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" t="n">
-        <v>-0.355576586281534</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" t="n">
-        <v>-0.653365130572011</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-1.78051213864203</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" t="n">
-        <v>-0.566552839960856</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" t="n">
-        <v>-1.19485579916184</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" t="n">
-        <v>-1.11983459083066</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" t="n">
-        <v>0.00498428241932736</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>15</v>
-      </c>
-      <c r="B30" t="s">
-        <v>16</v>
-      </c>
-      <c r="C30" t="n">
-        <v>-0.175667016328348</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" t="n">
-        <v>-0.220627963714533</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>15</v>
-      </c>
-      <c r="B32" t="s">
-        <v>16</v>
-      </c>
-      <c r="C32" t="n">
-        <v>-0.330497312700578</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C33" t="n">
-        <v>-0.20160865861586</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>15</v>
-      </c>
-      <c r="B34" t="s">
-        <v>16</v>
-      </c>
-      <c r="C34" t="n">
-        <v>-0.899293004638937</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>15</v>
-      </c>
-      <c r="B35" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" t="n">
-        <v>0.26328992024772</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>15</v>
-      </c>
-      <c r="B36" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36" t="n">
-        <v>-0.870137721928433</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>15</v>
-      </c>
-      <c r="B37" t="s">
-        <v>16</v>
-      </c>
-      <c r="C37" t="n">
-        <v>0.559754650769003</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>15</v>
-      </c>
-      <c r="B38" t="s">
-        <v>16</v>
-      </c>
-      <c r="C38" t="n">
-        <v>0.341295667472</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>15</v>
-      </c>
-      <c r="B39" t="s">
-        <v>16</v>
-      </c>
-      <c r="C39" t="n">
-        <v>-1.05493381530671</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>15</v>
-      </c>
-      <c r="B40" t="s">
-        <v>16</v>
-      </c>
-      <c r="C40" t="n">
-        <v>-0.627456504975449</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>15</v>
-      </c>
-      <c r="B41" t="s">
-        <v>16</v>
-      </c>
-      <c r="C41" t="n">
-        <v>-0.700833986426558</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s">
-        <v>15</v>
-      </c>
-      <c r="B42" t="s">
-        <v>16</v>
-      </c>
-      <c r="C42" t="n">
-        <v>-1.00451300963058</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s">
-        <v>15</v>
-      </c>
-      <c r="B43" t="s">
-        <v>16</v>
-      </c>
-      <c r="C43" t="n">
-        <v>-1.39322722615888</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s">
-        <v>15</v>
-      </c>
-      <c r="B44" t="s">
-        <v>16</v>
-      </c>
-      <c r="C44" t="n">
-        <v>-0.275350988642695</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s">
-        <v>15</v>
-      </c>
-      <c r="B45" t="s">
-        <v>16</v>
-      </c>
-      <c r="C45" t="n">
-        <v>-0.792634436258761</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46" t="s">
-        <v>16</v>
-      </c>
-      <c r="C46" t="n">
-        <v>-1.32917449938461</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s">
-        <v>15</v>
-      </c>
-      <c r="B47" t="s">
-        <v>16</v>
-      </c>
-      <c r="C47" t="n">
-        <v>-0.442281529499913</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s">
-        <v>15</v>
-      </c>
-      <c r="B48" t="s">
-        <v>16</v>
-      </c>
-      <c r="C48" t="n">
-        <v>-0.0773802655230915</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s">
-        <v>15</v>
-      </c>
-      <c r="B49" t="s">
-        <v>16</v>
-      </c>
-      <c r="C49" t="n">
-        <v>-0.122452480601785</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s">
-        <v>15</v>
-      </c>
-      <c r="B50" t="s">
-        <v>16</v>
-      </c>
-      <c r="C50" t="n">
-        <v>-1.07850120763492</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s">
-        <v>15</v>
-      </c>
-      <c r="B51" t="s">
-        <v>16</v>
-      </c>
-      <c r="C51" t="n">
-        <v>-1.57104833009141</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s">
-        <v>15</v>
-      </c>
-      <c r="B52" t="s">
-        <v>16</v>
-      </c>
-      <c r="C52" t="n">
-        <v>-1.3572855183662</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s">
-        <v>15</v>
-      </c>
-      <c r="B53" t="s">
-        <v>16</v>
-      </c>
-      <c r="C53" t="n">
-        <v>0.190986707273051</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s">
-        <v>15</v>
-      </c>
-      <c r="B54" t="s">
-        <v>16</v>
-      </c>
-      <c r="C54" t="n">
-        <v>0.17505069925429</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s">
-        <v>15</v>
-      </c>
-      <c r="B55" t="s">
-        <v>16</v>
-      </c>
-      <c r="C55" t="n">
-        <v>-1.22098807141178</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s">
-        <v>15</v>
-      </c>
-      <c r="B56" t="s">
-        <v>16</v>
-      </c>
-      <c r="C56" t="n">
-        <v>0.289594048963098</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s">
-        <v>15</v>
-      </c>
-      <c r="B57" t="s">
-        <v>16</v>
-      </c>
-      <c r="C57" t="n">
-        <v>-2.23880516565358</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s">
-        <v>15</v>
-      </c>
-      <c r="B58" t="s">
-        <v>16</v>
-      </c>
-      <c r="C58" t="n">
-        <v>-2.37354774601245</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s">
-        <v>15</v>
-      </c>
-      <c r="B59" t="s">
-        <v>16</v>
-      </c>
-      <c r="C59" t="n">
-        <v>0.173169226199882</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s">
-        <v>15</v>
-      </c>
-      <c r="B60" t="s">
-        <v>16</v>
-      </c>
-      <c r="C60" t="n">
-        <v>-0.0511753817905642</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s">
-        <v>15</v>
-      </c>
-      <c r="B61" t="s">
-        <v>16</v>
-      </c>
-      <c r="C61" t="n">
-        <v>-1.03256631421804</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s">
-        <v>15</v>
-      </c>
-      <c r="B62" t="s">
-        <v>16</v>
-      </c>
-      <c r="C62" t="n">
-        <v>-2.52374161124019</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s">
-        <v>15</v>
-      </c>
-      <c r="B63" t="s">
-        <v>16</v>
-      </c>
-      <c r="C63" t="n">
-        <v>-1.28611626107244</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s">
-        <v>15</v>
-      </c>
-      <c r="B64" t="s">
-        <v>16</v>
-      </c>
-      <c r="C64" t="n">
-        <v>-0.371732426827283</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s">
-        <v>15</v>
-      </c>
-      <c r="B65" t="s">
-        <v>16</v>
-      </c>
-      <c r="C65" t="n">
-        <v>-1.10780193604033</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s">
-        <v>15</v>
-      </c>
-      <c r="B66" t="s">
-        <v>16</v>
-      </c>
-      <c r="C66" t="n">
-        <v>-1.19645067676236</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s">
-        <v>15</v>
-      </c>
-      <c r="B67" t="s">
-        <v>16</v>
-      </c>
-      <c r="C67" t="n">
-        <v>-3.04455051604412</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s">
-        <v>15</v>
-      </c>
-      <c r="B68" t="s">
-        <v>16</v>
-      </c>
-      <c r="C68" t="n">
-        <v>-0.448228824989066</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
-        <v>15</v>
-      </c>
-      <c r="B69" t="s">
-        <v>16</v>
-      </c>
-      <c r="C69" t="n">
-        <v>0.114380710644853</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>15</v>
-      </c>
-      <c r="B70" t="s">
-        <v>16</v>
-      </c>
-      <c r="C70" t="n">
-        <v>-1.4854870132426</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s">
-        <v>15</v>
-      </c>
-      <c r="B71" t="s">
-        <v>16</v>
-      </c>
-      <c r="C71" t="n">
-        <v>-0.426254428894678</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s">
-        <v>15</v>
-      </c>
-      <c r="B72" t="s">
-        <v>16</v>
-      </c>
-      <c r="C72" t="n">
-        <v>-0.333756627868314</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s">
-        <v>15</v>
-      </c>
-      <c r="B73" t="s">
-        <v>16</v>
-      </c>
-      <c r="C73" t="n">
-        <v>-0.96344716631637</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s">
-        <v>15</v>
-      </c>
-      <c r="B74" t="s">
-        <v>16</v>
-      </c>
-      <c r="C74" t="n">
-        <v>-0.516855646434006</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s">
-        <v>15</v>
-      </c>
-      <c r="B75" t="s">
-        <v>16</v>
-      </c>
-      <c r="C75" t="n">
-        <v>-0.603946454074886</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s">
-        <v>15</v>
-      </c>
-      <c r="B76" t="s">
-        <v>16</v>
-      </c>
-      <c r="C76" t="n">
-        <v>-0.283934398728876</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s">
-        <v>15</v>
-      </c>
-      <c r="B77" t="s">
-        <v>16</v>
-      </c>
-      <c r="C77" t="n">
-        <v>0.0995764642194759</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s">
-        <v>15</v>
-      </c>
-      <c r="B78" t="s">
-        <v>16</v>
-      </c>
-      <c r="C78" t="n">
-        <v>-0.48844068251733</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s">
-        <v>15</v>
-      </c>
-      <c r="B79" t="s">
-        <v>16</v>
-      </c>
-      <c r="C79" t="n">
-        <v>0.31040162362996</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s">
-        <v>15</v>
-      </c>
-      <c r="B80" t="s">
-        <v>16</v>
-      </c>
-      <c r="C80" t="n">
-        <v>-0.908057357022236</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s">
-        <v>15</v>
-      </c>
-      <c r="B81" t="s">
-        <v>16</v>
-      </c>
-      <c r="C81" t="n">
-        <v>0.2831741672851</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s">
-        <v>15</v>
-      </c>
-      <c r="B82" t="s">
-        <v>16</v>
-      </c>
-      <c r="C82" t="n">
-        <v>-1.04716816482427</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s">
-        <v>15</v>
-      </c>
-      <c r="B83" t="s">
-        <v>16</v>
-      </c>
-      <c r="C83" t="n">
-        <v>-0.307413329674751</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s">
-        <v>15</v>
-      </c>
-      <c r="B84" t="s">
-        <v>16</v>
-      </c>
-      <c r="C84" t="n">
-        <v>0.151995070896966</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s">
-        <v>15</v>
-      </c>
-      <c r="B85" t="s">
-        <v>16</v>
-      </c>
-      <c r="C85" t="n">
-        <v>-0.65558526990791</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s">
-        <v>15</v>
-      </c>
-      <c r="B86" t="s">
-        <v>16</v>
-      </c>
-      <c r="C86" t="n">
-        <v>-0.871776821604845</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s">
-        <v>15</v>
-      </c>
-      <c r="B87" t="s">
-        <v>16</v>
-      </c>
-      <c r="C87" t="n">
-        <v>-0.805705544553208</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s">
-        <v>15</v>
-      </c>
-      <c r="B88" t="s">
-        <v>16</v>
-      </c>
-      <c r="C88" t="n">
-        <v>-0.235446546156303</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s">
-        <v>15</v>
-      </c>
-      <c r="B89" t="s">
-        <v>16</v>
-      </c>
-      <c r="C89" t="n">
-        <v>-0.664480192144702</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s">
-        <v>15</v>
-      </c>
-      <c r="B90" t="s">
-        <v>16</v>
-      </c>
-      <c r="C90" t="n">
-        <v>-1.3313920806647</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s">
-        <v>15</v>
-      </c>
-      <c r="B91" t="s">
-        <v>16</v>
-      </c>
-      <c r="C91" t="n">
-        <v>-0.800058011122912</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s">
-        <v>15</v>
-      </c>
-      <c r="B92" t="s">
-        <v>16</v>
-      </c>
-      <c r="C92" t="n">
-        <v>-0.0614816107190332</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="s">
-        <v>15</v>
-      </c>
-      <c r="B93" t="s">
-        <v>16</v>
-      </c>
-      <c r="C93" t="n">
-        <v>-2.86428848841393</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s">
-        <v>15</v>
-      </c>
-      <c r="B94" t="s">
-        <v>16</v>
-      </c>
-      <c r="C94" t="n">
-        <v>-1.35572819280547</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s">
-        <v>15</v>
-      </c>
-      <c r="B95" t="s">
-        <v>16</v>
-      </c>
-      <c r="C95" t="n">
-        <v>0.231171977709363</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="s">
-        <v>15</v>
-      </c>
-      <c r="B96" t="s">
-        <v>16</v>
-      </c>
-      <c r="C96" t="n">
-        <v>-0.138883489650657</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="s">
-        <v>15</v>
-      </c>
-      <c r="B97" t="s">
-        <v>16</v>
-      </c>
-      <c r="C97" t="n">
-        <v>-0.999254249061858</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s">
-        <v>15</v>
-      </c>
-      <c r="B98" t="s">
-        <v>16</v>
-      </c>
-      <c r="C98" t="n">
-        <v>-0.562281623697484</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="s">
-        <v>15</v>
-      </c>
-      <c r="B99" t="s">
-        <v>16</v>
-      </c>
-      <c r="C99" t="n">
-        <v>-0.172809905555753</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="s">
-        <v>15</v>
-      </c>
-      <c r="B100" t="s">
-        <v>16</v>
-      </c>
-      <c r="C100" t="n">
-        <v>0.0851367525382625</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s">
-        <v>15</v>
-      </c>
-      <c r="B101" t="s">
-        <v>16</v>
-      </c>
-      <c r="C101" t="n">
-        <v>-0.222354082657456</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s">
-        <v>15</v>
-      </c>
-      <c r="B102" t="s">
-        <v>16</v>
-      </c>
-      <c r="C102" t="n">
-        <v>-1.01460053245933</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s">
-        <v>15</v>
-      </c>
-      <c r="B103" t="s">
-        <v>16</v>
-      </c>
-      <c r="C103" t="n">
-        <v>0.475714500885432</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="s">
-        <v>15</v>
-      </c>
-      <c r="B104" t="s">
-        <v>16</v>
-      </c>
-      <c r="C104" t="n">
-        <v>-0.202213495034768</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="s">
-        <v>15</v>
-      </c>
-      <c r="B105" t="s">
-        <v>16</v>
-      </c>
-      <c r="C105" t="n">
-        <v>-0.276264805230566</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="s">
-        <v>15</v>
-      </c>
-      <c r="B106" t="s">
-        <v>16</v>
-      </c>
-      <c r="C106" t="n">
-        <v>-0.320255618616946</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="s">
-        <v>15</v>
-      </c>
-      <c r="B107" t="s">
-        <v>16</v>
-      </c>
-      <c r="C107" t="n">
-        <v>-1.19569792831868</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="s">
-        <v>15</v>
-      </c>
-      <c r="B108" t="s">
-        <v>16</v>
-      </c>
-      <c r="C108" t="n">
-        <v>-0.513283094479234</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s">
-        <v>15</v>
-      </c>
-      <c r="B109" t="s">
-        <v>16</v>
-      </c>
-      <c r="C109" t="n">
-        <v>0.215251720628851</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="s">
-        <v>15</v>
-      </c>
-      <c r="B110" t="s">
-        <v>16</v>
-      </c>
-      <c r="C110" t="n">
-        <v>0.117664402797231</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="s">
-        <v>15</v>
-      </c>
-      <c r="B111" t="s">
-        <v>16</v>
-      </c>
-      <c r="C111" t="n">
-        <v>-0.735727426417936</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="s">
-        <v>15</v>
-      </c>
-      <c r="B112" t="s">
-        <v>16</v>
-      </c>
-      <c r="C112" t="n">
-        <v>-0.232414804405075</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="s">
-        <v>15</v>
-      </c>
-      <c r="B113" t="s">
-        <v>16</v>
-      </c>
-      <c r="C113" t="n">
-        <v>-1.11291065474683</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="s">
-        <v>15</v>
-      </c>
-      <c r="B114" t="s">
-        <v>16</v>
-      </c>
-      <c r="C114" t="n">
-        <v>-0.735851119030469</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="s">
-        <v>15</v>
-      </c>
-      <c r="B115" t="s">
-        <v>16</v>
-      </c>
-      <c r="C115" t="n">
-        <v>-0.314733830307504</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="s">
-        <v>15</v>
-      </c>
-      <c r="B116" t="s">
-        <v>16</v>
-      </c>
-      <c r="C116" t="n">
-        <v>-1.32951324179087</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="s">
-        <v>15</v>
-      </c>
-      <c r="B117" t="s">
-        <v>16</v>
-      </c>
-      <c r="C117" t="n">
-        <v>-1.68094838689343</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="s">
-        <v>15</v>
-      </c>
-      <c r="B118" t="s">
-        <v>16</v>
-      </c>
-      <c r="C118" t="n">
-        <v>-0.521780976219</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="s">
-        <v>15</v>
-      </c>
-      <c r="B119" t="s">
-        <v>16</v>
-      </c>
-      <c r="C119" t="n">
-        <v>-2.5975253487322</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="s">
-        <v>15</v>
-      </c>
-      <c r="B120" t="s">
-        <v>16</v>
-      </c>
-      <c r="C120" t="n">
-        <v>-0.786407602955976</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="s">
-        <v>15</v>
-      </c>
-      <c r="B121" t="s">
-        <v>16</v>
-      </c>
-      <c r="C121" t="n">
-        <v>-0.140432632329928</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="s">
-        <v>15</v>
-      </c>
-      <c r="B122" t="s">
-        <v>16</v>
-      </c>
-      <c r="C122" t="n">
-        <v>-0.582128797844795</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="s">
-        <v>15</v>
-      </c>
-      <c r="B123" t="s">
-        <v>16</v>
-      </c>
-      <c r="C123" t="n">
-        <v>-1.07052227145855</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="s">
-        <v>15</v>
-      </c>
-      <c r="B124" t="s">
-        <v>16</v>
-      </c>
-      <c r="C124" t="n">
-        <v>-0.266985240153562</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="s">
-        <v>15</v>
-      </c>
-      <c r="B125" t="s">
-        <v>16</v>
-      </c>
-      <c r="C125" t="n">
-        <v>-0.319722784137134</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="s">
-        <v>15</v>
-      </c>
-      <c r="B126" t="s">
-        <v>16</v>
-      </c>
-      <c r="C126" t="n">
-        <v>0.0718219830151344</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="s">
-        <v>15</v>
-      </c>
-      <c r="B127" t="s">
-        <v>16</v>
-      </c>
-      <c r="C127" t="n">
-        <v>-0.0849941984089075</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="s">
-        <v>15</v>
-      </c>
-      <c r="B128" t="s">
-        <v>16</v>
-      </c>
-      <c r="C128" t="n">
-        <v>-0.571823329843994</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="s">
-        <v>15</v>
-      </c>
-      <c r="B129" t="s">
-        <v>16</v>
-      </c>
-      <c r="C129" t="n">
-        <v>-0.997175722491611</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="s">
-        <v>15</v>
-      </c>
-      <c r="B130" t="s">
-        <v>16</v>
-      </c>
-      <c r="C130" t="n">
-        <v>-1.39972906997075</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="s">
-        <v>15</v>
-      </c>
-      <c r="B131" t="s">
-        <v>16</v>
-      </c>
-      <c r="C131" t="n">
-        <v>-1.08282621089624</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="s">
-        <v>15</v>
-      </c>
-      <c r="B132" t="s">
-        <v>16</v>
-      </c>
-      <c r="C132" t="n">
-        <v>-0.659915450071319</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="s">
-        <v>15</v>
-      </c>
-      <c r="B133" t="s">
-        <v>16</v>
-      </c>
-      <c r="C133" t="n">
-        <v>-0.393870807174465</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="s">
-        <v>15</v>
-      </c>
-      <c r="B134" t="s">
-        <v>16</v>
-      </c>
-      <c r="C134" t="n">
-        <v>-1.22256114104654</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="s">
-        <v>15</v>
-      </c>
-      <c r="B135" t="s">
-        <v>16</v>
-      </c>
-      <c r="C135" t="n">
-        <v>-0.915111038023301</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="s">
-        <v>15</v>
-      </c>
-      <c r="B136" t="s">
-        <v>16</v>
-      </c>
-      <c r="C136" t="n">
-        <v>0.110059060600615</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="s">
-        <v>15</v>
-      </c>
-      <c r="B137" t="s">
-        <v>16</v>
-      </c>
-      <c r="C137" t="n">
-        <v>-1.30860052557213</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="s">
-        <v>15</v>
-      </c>
-      <c r="B138" t="s">
-        <v>16</v>
-      </c>
-      <c r="C138" t="n">
-        <v>0.117320882000334</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="s">
-        <v>15</v>
-      </c>
-      <c r="B139" t="s">
-        <v>16</v>
-      </c>
-      <c r="C139" t="n">
-        <v>-0.53772953402905</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="s">
-        <v>15</v>
-      </c>
-      <c r="B140" t="s">
-        <v>16</v>
-      </c>
-      <c r="C140" t="n">
-        <v>-0.761200525915486</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="s">
-        <v>15</v>
-      </c>
-      <c r="B141" t="s">
-        <v>16</v>
-      </c>
-      <c r="C141" t="n">
-        <v>-1.35875467993268</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="s">
-        <v>15</v>
-      </c>
-      <c r="B142" t="s">
-        <v>16</v>
-      </c>
-      <c r="C142" t="n">
-        <v>-1.06034211186824</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="s">
-        <v>15</v>
-      </c>
-      <c r="B143" t="s">
-        <v>16</v>
-      </c>
-      <c r="C143" t="n">
-        <v>0.0384558187721458</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="s">
-        <v>15</v>
-      </c>
-      <c r="B144" t="s">
-        <v>16</v>
-      </c>
-      <c r="C144" t="n">
-        <v>-1.32273662503595</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="s">
-        <v>15</v>
-      </c>
-      <c r="B145" t="s">
-        <v>16</v>
-      </c>
-      <c r="C145" t="n">
-        <v>-0.724432847898264</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="s">
-        <v>15</v>
-      </c>
-      <c r="B146" t="s">
-        <v>16</v>
-      </c>
-      <c r="C146" t="n">
-        <v>-0.822893470395851</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="s">
-        <v>15</v>
-      </c>
-      <c r="B147" t="s">
-        <v>16</v>
-      </c>
-      <c r="C147" t="n">
-        <v>-0.476299422798959</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="s">
-        <v>15</v>
-      </c>
-      <c r="B148" t="s">
-        <v>16</v>
-      </c>
-      <c r="C148" t="n">
-        <v>-1.24577969304979</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="s">
-        <v>15</v>
-      </c>
-      <c r="B149" t="s">
-        <v>16</v>
-      </c>
-      <c r="C149" t="n">
-        <v>-0.685603762351511</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="s">
-        <v>15</v>
-      </c>
-      <c r="B150" t="s">
-        <v>16</v>
-      </c>
-      <c r="C150" t="n">
-        <v>-0.0115089988222272</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="s">
-        <v>15</v>
-      </c>
-      <c r="B151" t="s">
-        <v>16</v>
-      </c>
-      <c r="C151" t="n">
-        <v>-0.63349475055148</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="s">
-        <v>15</v>
-      </c>
-      <c r="B152" t="s">
-        <v>16</v>
-      </c>
-      <c r="C152" t="n">
-        <v>-0.851968384622722</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="s">
-        <v>15</v>
-      </c>
-      <c r="B153" t="s">
-        <v>16</v>
-      </c>
-      <c r="C153" t="n">
-        <v>-0.559662572293591</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="s">
-        <v>15</v>
-      </c>
-      <c r="B154" t="s">
-        <v>16</v>
-      </c>
-      <c r="C154" t="n">
-        <v>-0.0360683069721717</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="s">
-        <v>15</v>
-      </c>
-      <c r="B155" t="s">
-        <v>16</v>
-      </c>
-      <c r="C155" t="n">
-        <v>-1.2316894756905</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="s">
-        <v>15</v>
-      </c>
-      <c r="B156" t="s">
-        <v>16</v>
-      </c>
-      <c r="C156" t="n">
-        <v>-0.202715348348802</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="s">
-        <v>15</v>
-      </c>
-      <c r="B157" t="s">
-        <v>16</v>
-      </c>
-      <c r="C157" t="n">
-        <v>-0.213149425881049</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="s">
-        <v>15</v>
-      </c>
-      <c r="B158" t="s">
-        <v>16</v>
-      </c>
-      <c r="C158" t="n">
-        <v>-0.623563980079168</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="s">
-        <v>15</v>
-      </c>
-      <c r="B159" t="s">
-        <v>16</v>
-      </c>
-      <c r="C159" t="n">
-        <v>-0.701417642631009</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s">
-        <v>15</v>
-      </c>
-      <c r="B160" t="s">
-        <v>16</v>
-      </c>
-      <c r="C160" t="n">
-        <v>-0.25380262618631</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="s">
-        <v>15</v>
-      </c>
-      <c r="B161" t="s">
-        <v>16</v>
-      </c>
-      <c r="C161" t="n">
-        <v>-1.29443344417838</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="s">
-        <v>15</v>
-      </c>
-      <c r="B162" t="s">
-        <v>16</v>
-      </c>
-      <c r="C162" t="n">
-        <v>0.483760657076049</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="s">
-        <v>15</v>
-      </c>
-      <c r="B163" t="s">
-        <v>16</v>
-      </c>
-      <c r="C163" t="n">
-        <v>-0.13856941112041</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="s">
-        <v>15</v>
-      </c>
-      <c r="B164" t="s">
-        <v>16</v>
-      </c>
-      <c r="C164" t="n">
-        <v>-0.526884930171791</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="s">
-        <v>15</v>
-      </c>
-      <c r="B165" t="s">
-        <v>16</v>
-      </c>
-      <c r="C165" t="n">
-        <v>-0.361538687614868</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="s">
-        <v>15</v>
-      </c>
-      <c r="B166" t="s">
-        <v>16</v>
-      </c>
-      <c r="C166" t="n">
-        <v>-0.385398759223392</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="s">
-        <v>15</v>
-      </c>
-      <c r="B167" t="s">
-        <v>16</v>
-      </c>
-      <c r="C167" t="n">
-        <v>-1.26436516303931</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="s">
-        <v>15</v>
-      </c>
-      <c r="B168" t="s">
-        <v>16</v>
-      </c>
-      <c r="C168" t="n">
-        <v>-0.506601466443003</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="s">
-        <v>15</v>
-      </c>
-      <c r="B169" t="s">
-        <v>16</v>
-      </c>
-      <c r="C169" t="n">
-        <v>0.294924900756128</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="s">
-        <v>15</v>
-      </c>
-      <c r="B170" t="s">
-        <v>16</v>
-      </c>
-      <c r="C170" t="n">
-        <v>-0.330973536184646</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="s">
-        <v>15</v>
-      </c>
-      <c r="B171" t="s">
-        <v>16</v>
-      </c>
-      <c r="C171" t="n">
-        <v>-0.153935739691228</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="s">
-        <v>15</v>
-      </c>
-      <c r="B172" t="s">
-        <v>16</v>
-      </c>
-      <c r="C172" t="n">
-        <v>-1.69387367265109</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="s">
-        <v>15</v>
-      </c>
-      <c r="B173" t="s">
-        <v>16</v>
-      </c>
-      <c r="C173" t="n">
-        <v>-1.04427804721607</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="s">
-        <v>15</v>
-      </c>
-      <c r="B174" t="s">
-        <v>16</v>
-      </c>
-      <c r="C174" t="n">
-        <v>-1.5078019352487</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="s">
-        <v>15</v>
-      </c>
-      <c r="B175" t="s">
-        <v>16</v>
-      </c>
-      <c r="C175" t="n">
-        <v>-0.183904075228955</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="s">
-        <v>15</v>
-      </c>
-      <c r="B176" t="s">
-        <v>16</v>
-      </c>
-      <c r="C176" t="n">
-        <v>-0.815998105486749</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="s">
-        <v>15</v>
-      </c>
-      <c r="B177" t="s">
-        <v>16</v>
-      </c>
-      <c r="C177" t="n">
-        <v>-1.28557820711627</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="s">
-        <v>15</v>
-      </c>
-      <c r="B178" t="s">
-        <v>16</v>
-      </c>
-      <c r="C178" t="n">
-        <v>-0.301756652022842</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="s">
-        <v>15</v>
-      </c>
-      <c r="B179" t="s">
-        <v>16</v>
-      </c>
-      <c r="C179" t="n">
-        <v>-0.953003823228175</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="s">
-        <v>15</v>
-      </c>
-      <c r="B180" t="s">
-        <v>16</v>
-      </c>
-      <c r="C180" t="n">
-        <v>0.294820512030144</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="s">
-        <v>15</v>
-      </c>
-      <c r="B181" t="s">
-        <v>16</v>
-      </c>
-      <c r="C181" t="n">
-        <v>-0.908284543237646</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="s">
-        <v>15</v>
-      </c>
-      <c r="B182" t="s">
-        <v>16</v>
-      </c>
-      <c r="C182" t="n">
-        <v>-1.77996678548736</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="s">
-        <v>15</v>
-      </c>
-      <c r="B183" t="s">
-        <v>16</v>
-      </c>
-      <c r="C183" t="n">
-        <v>-0.892210068350537</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="s">
-        <v>15</v>
-      </c>
-      <c r="B184" t="s">
-        <v>16</v>
-      </c>
-      <c r="C184" t="n">
-        <v>-0.130125901113096</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="s">
-        <v>15</v>
-      </c>
-      <c r="B185" t="s">
-        <v>16</v>
-      </c>
-      <c r="C185" t="n">
-        <v>-0.608220512020406</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="s">
-        <v>15</v>
-      </c>
-      <c r="B186" t="s">
-        <v>16</v>
-      </c>
-      <c r="C186" t="n">
-        <v>0.253603362258549</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="s">
-        <v>15</v>
-      </c>
-      <c r="B187" t="s">
-        <v>16</v>
-      </c>
-      <c r="C187" t="n">
-        <v>0.156463023277289</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="s">
-        <v>15</v>
-      </c>
-      <c r="B188" t="s">
-        <v>16</v>
-      </c>
-      <c r="C188" t="n">
-        <v>-0.0582821187566527</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="s">
-        <v>15</v>
-      </c>
-      <c r="B189" t="s">
-        <v>16</v>
-      </c>
-      <c r="C189" t="n">
-        <v>-0.201115332532624</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="s">
-        <v>15</v>
-      </c>
-      <c r="B190" t="s">
-        <v>16</v>
-      </c>
-      <c r="C190" t="n">
-        <v>-0.39669528393414</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="s">
-        <v>15</v>
-      </c>
-      <c r="B191" t="s">
-        <v>16</v>
-      </c>
-      <c r="C191" t="n">
-        <v>0.037735338530294</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="s">
-        <v>15</v>
-      </c>
-      <c r="B192" t="s">
-        <v>16</v>
-      </c>
-      <c r="C192" t="n">
-        <v>-0.316825472754897</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="s">
-        <v>15</v>
-      </c>
-      <c r="B193" t="s">
-        <v>16</v>
-      </c>
-      <c r="C193" t="n">
-        <v>-0.7361706941571</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="s">
-        <v>15</v>
-      </c>
-      <c r="B194" t="s">
-        <v>16</v>
-      </c>
-      <c r="C194" t="n">
-        <v>-0.128625294827914</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="s">
-        <v>15</v>
-      </c>
-      <c r="B195" t="s">
-        <v>16</v>
-      </c>
-      <c r="C195" t="n">
-        <v>-0.233481027142751</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="s">
-        <v>15</v>
-      </c>
-      <c r="B196" t="s">
-        <v>16</v>
-      </c>
-      <c r="C196" t="n">
-        <v>-1.27698518339052</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="s">
-        <v>15</v>
-      </c>
-      <c r="B197" t="s">
-        <v>16</v>
-      </c>
-      <c r="C197" t="n">
-        <v>-0.730635160138615</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="s">
-        <v>15</v>
-      </c>
-      <c r="B198" t="s">
-        <v>16</v>
-      </c>
-      <c r="C198" t="n">
-        <v>-0.936691981905753</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="s">
-        <v>15</v>
-      </c>
-      <c r="B199" t="s">
-        <v>16</v>
-      </c>
-      <c r="C199" t="n">
-        <v>0.124609361227393</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="s">
-        <v>15</v>
-      </c>
-      <c r="B200" t="s">
-        <v>16</v>
-      </c>
-      <c r="C200" t="n">
-        <v>-0.121899766432122</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="s">
-        <v>15</v>
-      </c>
-      <c r="B201" t="s">
-        <v>16</v>
-      </c>
-      <c r="C201" t="n">
-        <v>-0.31228651993578</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -3250,7 +1063,7 @@
         <v>9.43</v>
       </c>
       <c r="E2" t="n">
-        <v>5.82314636094472</v>
+        <v>5.89324338385411</v>
       </c>
     </row>
     <row r="3">
@@ -3267,7 +1080,7 @@
         <v>20.73</v>
       </c>
       <c r="E3" t="n">
-        <v>4.43930696955547</v>
+        <v>4.23931027911072</v>
       </c>
     </row>
     <row r="4">
@@ -3284,7 +1097,7 @@
         <v>13.69</v>
       </c>
       <c r="E4" t="n">
-        <v>1.15811526454789</v>
+        <v>1.09138368765951</v>
       </c>
     </row>
     <row r="5">
@@ -3301,7 +1114,7 @@
         <v>10.45</v>
       </c>
       <c r="E5" t="n">
-        <v>3.1944449882598</v>
+        <v>3.32743010957899</v>
       </c>
     </row>
     <row r="6">
@@ -3318,7 +1131,7 @@
         <v>14.93</v>
       </c>
       <c r="E6" t="n">
-        <v>30.6264775031074</v>
+        <v>29.0502102995453</v>
       </c>
     </row>
     <row r="7">
@@ -3335,7 +1148,7 @@
         <v>13.79</v>
       </c>
       <c r="E7" t="n">
-        <v>1.98802592810242</v>
+        <v>1.78094222542429</v>
       </c>
     </row>
     <row r="8">
@@ -3352,7 +1165,7 @@
         <v>8.06</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.626630477608742</v>
+        <v>-0.384961849883476</v>
       </c>
     </row>
     <row r="9">
@@ -3369,7 +1182,7 @@
         <v>0.79</v>
       </c>
       <c r="E9" t="n">
-        <v>11.7164923845208</v>
+        <v>11.6563314892341</v>
       </c>
     </row>
     <row r="10">
@@ -3386,7 +1199,7 @@
         <v>0.85</v>
       </c>
       <c r="E10" t="n">
-        <v>1.04728778811394</v>
+        <v>1.02782597909849</v>
       </c>
     </row>
     <row r="11">
@@ -3403,7 +1216,7 @@
         <v>-4.09</v>
       </c>
       <c r="E11" t="n">
-        <v>4.42410503031323</v>
+        <v>4.34884169574441</v>
       </c>
     </row>
     <row r="12">
@@ -3420,7 +1233,7 @@
         <v>-0.74</v>
       </c>
       <c r="E12" t="n">
-        <v>4.44795612999142</v>
+        <v>4.29869390942194</v>
       </c>
     </row>
     <row r="13">
@@ -3437,7 +1250,7 @@
         <v>-1.86</v>
       </c>
       <c r="E13" t="n">
-        <v>5.8258270960838</v>
+        <v>5.73360421234447</v>
       </c>
     </row>
     <row r="14">
@@ -3454,7 +1267,7 @@
         <v>-6.6</v>
       </c>
       <c r="E14" t="n">
-        <v>0.726642818890421</v>
+        <v>0.993539056563455</v>
       </c>
     </row>
     <row r="15">
@@ -3471,7 +1284,7 @@
         <v>-5.99</v>
       </c>
       <c r="E15" t="n">
-        <v>7.51226380727079</v>
+        <v>5.14984909530298</v>
       </c>
     </row>
     <row r="16">
@@ -3488,7 +1301,7 @@
         <v>-0.48</v>
       </c>
       <c r="E16" t="n">
-        <v>5.25789418408731</v>
+        <v>5.19912615436713</v>
       </c>
     </row>
   </sheetData>
@@ -3751,10 +1564,10 @@
         <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="16">
@@ -3768,10 +1581,10 @@
         <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="17">
@@ -3785,10 +1598,10 @@
         <v>53</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="18">
@@ -3802,10 +1615,10 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="19">
@@ -3819,10 +1632,10 @@
         <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="20">
@@ -3836,10 +1649,10 @@
         <v>56</v>
       </c>
       <c r="D20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="21">
@@ -3853,10 +1666,10 @@
         <v>57</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E21" t="n">
-        <v>0.733333333333333</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="22">
@@ -3870,10 +1683,10 @@
         <v>58</v>
       </c>
       <c r="D22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E22" t="n">
-        <v>0.733333333333333</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="23">
@@ -3887,10 +1700,10 @@
         <v>59</v>
       </c>
       <c r="D23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E23" t="n">
-        <v>0.733333333333333</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="24">
@@ -3904,10 +1717,10 @@
         <v>60</v>
       </c>
       <c r="D24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E24" t="n">
-        <v>0.733333333333333</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="25">
@@ -3972,10 +1785,10 @@
         <v>64</v>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E28" t="n">
-        <v>0.666666666666667</v>
+        <v>0.733333333333333</v>
       </c>
     </row>
     <row r="29">
@@ -3989,10 +1802,10 @@
         <v>65</v>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E29" t="n">
-        <v>0.666666666666667</v>
+        <v>0.733333333333333</v>
       </c>
     </row>
     <row r="30">
@@ -4006,10 +1819,10 @@
         <v>66</v>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E30" t="n">
-        <v>0.666666666666667</v>
+        <v>0.733333333333333</v>
       </c>
     </row>
     <row r="31">
@@ -4057,10 +1870,10 @@
         <v>69</v>
       </c>
       <c r="D33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E33" t="n">
-        <v>0.6</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="34">
@@ -4074,10 +1887,10 @@
         <v>70</v>
       </c>
       <c r="D34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E34" t="n">
-        <v>0.6</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="35">
@@ -4125,10 +1938,10 @@
         <v>73</v>
       </c>
       <c r="D37" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E37" t="n">
-        <v>0.533333333333333</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="38">
@@ -4142,10 +1955,10 @@
         <v>74</v>
       </c>
       <c r="D38" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E38" t="n">
-        <v>0.466666666666667</v>
+        <v>0.533333333333333</v>
       </c>
     </row>
     <row r="39">
@@ -4159,10 +1972,10 @@
         <v>75</v>
       </c>
       <c r="D39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E39" t="n">
-        <v>0.466666666666667</v>
+        <v>0.533333333333333</v>
       </c>
     </row>
     <row r="40">
@@ -4176,10 +1989,10 @@
         <v>76</v>
       </c>
       <c r="D40" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E40" t="n">
-        <v>0.4</v>
+        <v>0.466666666666667</v>
       </c>
     </row>
     <row r="41">
@@ -4193,10 +2006,10 @@
         <v>77</v>
       </c>
       <c r="D41" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E41" t="n">
-        <v>0.4</v>
+        <v>0.466666666666667</v>
       </c>
     </row>
     <row r="42">
@@ -4210,10 +2023,10 @@
         <v>78</v>
       </c>
       <c r="D42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E42" t="n">
-        <v>0.4</v>
+        <v>0.466666666666667</v>
       </c>
     </row>
     <row r="43">
@@ -4227,10 +2040,10 @@
         <v>79</v>
       </c>
       <c r="D43" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E43" t="n">
-        <v>0.4</v>
+        <v>0.466666666666667</v>
       </c>
     </row>
     <row r="44">
@@ -4261,10 +2074,10 @@
         <v>81</v>
       </c>
       <c r="D45" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E45" t="n">
-        <v>0.4</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="46">
@@ -4312,10 +2125,10 @@
         <v>84</v>
       </c>
       <c r="D48" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E48" t="n">
-        <v>0.333333333333333</v>
+        <v>0.266666666666667</v>
       </c>
     </row>
     <row r="49">
@@ -4380,10 +2193,10 @@
         <v>88</v>
       </c>
       <c r="D52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E52" t="n">
-        <v>0.2</v>
+        <v>0.266666666666667</v>
       </c>
     </row>
     <row r="53">
@@ -4397,10 +2210,10 @@
         <v>89</v>
       </c>
       <c r="D53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E53" t="n">
-        <v>0.2</v>
+        <v>0.266666666666667</v>
       </c>
     </row>
     <row r="54">
@@ -4567,10 +2380,10 @@
         <v>99</v>
       </c>
       <c r="D63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E63" t="n">
-        <v>0.133333333333333</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="64">
@@ -5862,6 +3675,125 @@
         <v>1</v>
       </c>
       <c r="E139" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>15</v>
+      </c>
+      <c r="B140" t="s">
+        <v>16</v>
+      </c>
+      <c r="C140" t="s">
+        <v>176</v>
+      </c>
+      <c r="D140" t="n">
+        <v>1</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>15</v>
+      </c>
+      <c r="B141" t="s">
+        <v>16</v>
+      </c>
+      <c r="C141" t="s">
+        <v>177</v>
+      </c>
+      <c r="D141" t="n">
+        <v>1</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>15</v>
+      </c>
+      <c r="B142" t="s">
+        <v>16</v>
+      </c>
+      <c r="C142" t="s">
+        <v>178</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>15</v>
+      </c>
+      <c r="B143" t="s">
+        <v>16</v>
+      </c>
+      <c r="C143" t="s">
+        <v>179</v>
+      </c>
+      <c r="D143" t="n">
+        <v>1</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>15</v>
+      </c>
+      <c r="B144" t="s">
+        <v>16</v>
+      </c>
+      <c r="C144" t="s">
+        <v>180</v>
+      </c>
+      <c r="D144" t="n">
+        <v>1</v>
+      </c>
+      <c r="E144" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>15</v>
+      </c>
+      <c r="B145" t="s">
+        <v>16</v>
+      </c>
+      <c r="C145" t="s">
+        <v>181</v>
+      </c>
+      <c r="D145" t="n">
+        <v>1</v>
+      </c>
+      <c r="E145" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>15</v>
+      </c>
+      <c r="B146" t="s">
+        <v>16</v>
+      </c>
+      <c r="C146" t="s">
+        <v>182</v>
+      </c>
+      <c r="D146" t="n">
+        <v>1</v>
+      </c>
+      <c r="E146" t="n">
         <v>0.0666666666666667</v>
       </c>
     </row>

--- a/05_Figures/F06_prediction/proteins/acute/comp_hypertrophy/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/acute/comp_hypertrophy/spls/c_data/results.xlsx
@@ -986,7 +986,7 @@
         <v>1900</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H3" t="n">
         <v>-0.341308375411348</v>
@@ -994,10 +994,18 @@
       <c r="I3" t="n">
         <v>-0.00714285714285714</v>
       </c>
-      <c r="J3"/>
-      <c r="K3"/>
-      <c r="L3"/>
-      <c r="M3"/>
+      <c r="J3" t="n">
+        <v>0.388059701492537</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.388059701492537</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.628948238004352</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.703583265318801</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1021,6 +1029,2206 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.257391085354592</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.027898454232899</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-3.36433722482098</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.234731018784395</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.665179161264095</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.42012274118049</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-1.97945326456668</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-1.39398465844497</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.839241433026241</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-1.05712554418816</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.727632801002082</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.525948325736153</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.160073873911798</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-1.85466684180872</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.0927471837435899</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-3.41272153761919</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.615050668680686</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.437363090325386</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-0.182524797814818</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-1.2318502976774</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-0.854332816566679</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-0.40870966891279</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-0.416919705686501</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-1.87624791620987</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="n">
+        <v>-0.686975019424994</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-0.627978602187413</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" t="n">
+        <v>-1.31441712601182</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" t="n">
+        <v>-0.0644258300132465</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-0.63052662042598</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" t="n">
+        <v>-0.294565898584821</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-0.322166626306224</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-0.257363222320293</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-0.94502355812897</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.28152856466587</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-0.896361282388483</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.563681155392</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.305973512328474</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-0.84975373893852</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" t="n">
+        <v>-0.570382114005039</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" t="n">
+        <v>-0.691720802613607</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" t="n">
+        <v>-0.606177630840535</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" t="n">
+        <v>-1.5417798475607</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" t="n">
+        <v>-0.232878313849432</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" t="n">
+        <v>-0.60744753526132</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" t="n">
+        <v>-0.862244074552093</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" t="n">
+        <v>-0.410217265237635</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>15</v>
+      </c>
+      <c r="B48" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" t="n">
+        <v>-0.129356088986699</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" t="n">
+        <v>-0.109423489746522</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" t="n">
+        <v>-1.30837204175606</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" t="n">
+        <v>-0.771555988886482</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52" t="n">
+        <v>-1.57679851345061</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53" t="s">
+        <v>16</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.176099896056104</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>15</v>
+      </c>
+      <c r="B54" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.308881821119121</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" t="n">
+        <v>-1.45639598845046</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.280025548846252</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>15</v>
+      </c>
+      <c r="B57" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" t="n">
+        <v>-2.24969641659461</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>15</v>
+      </c>
+      <c r="B58" t="s">
+        <v>16</v>
+      </c>
+      <c r="C58" t="n">
+        <v>-1.24582072688214</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.131331021919208</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>15</v>
+      </c>
+      <c r="B60" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" t="n">
+        <v>-0.01336056939841</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61" t="n">
+        <v>-2.22095751168687</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>15</v>
+      </c>
+      <c r="B62" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" t="n">
+        <v>-2.62345841355311</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>15</v>
+      </c>
+      <c r="B63" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63" t="n">
+        <v>-1.23503083398675</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>15</v>
+      </c>
+      <c r="B64" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" t="n">
+        <v>-0.297604851277199</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>15</v>
+      </c>
+      <c r="B65" t="s">
+        <v>16</v>
+      </c>
+      <c r="C65" t="n">
+        <v>-1.12113609205037</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>15</v>
+      </c>
+      <c r="B66" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" t="n">
+        <v>-1.13146871500731</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>15</v>
+      </c>
+      <c r="B67" t="s">
+        <v>16</v>
+      </c>
+      <c r="C67" t="n">
+        <v>-2.95259903703537</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>15</v>
+      </c>
+      <c r="B68" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" t="n">
+        <v>-0.356468593675031</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>15</v>
+      </c>
+      <c r="B69" t="s">
+        <v>16</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0.226904883509073</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>15</v>
+      </c>
+      <c r="B70" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" t="n">
+        <v>-1.28781702461286</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>15</v>
+      </c>
+      <c r="B71" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" t="n">
+        <v>-0.462416865122171</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>15</v>
+      </c>
+      <c r="B72" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" t="n">
+        <v>-0.376850113680618</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>15</v>
+      </c>
+      <c r="B73" t="s">
+        <v>16</v>
+      </c>
+      <c r="C73" t="n">
+        <v>-0.952523031172823</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>15</v>
+      </c>
+      <c r="B74" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" t="n">
+        <v>-0.477185314809078</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>15</v>
+      </c>
+      <c r="B75" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" t="n">
+        <v>-0.236021403691742</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>15</v>
+      </c>
+      <c r="B76" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" t="n">
+        <v>-0.495895272239448</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>15</v>
+      </c>
+      <c r="B77" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0.149822786980336</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>15</v>
+      </c>
+      <c r="B78" t="s">
+        <v>16</v>
+      </c>
+      <c r="C78" t="n">
+        <v>-0.527925687221943</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>15</v>
+      </c>
+      <c r="B79" t="s">
+        <v>16</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0.409197899419747</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>15</v>
+      </c>
+      <c r="B80" t="s">
+        <v>16</v>
+      </c>
+      <c r="C80" t="n">
+        <v>-0.812325862097699</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>15</v>
+      </c>
+      <c r="B81" t="s">
+        <v>16</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0.180419838027154</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>15</v>
+      </c>
+      <c r="B82" t="s">
+        <v>16</v>
+      </c>
+      <c r="C82" t="n">
+        <v>-0.910989461008861</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>15</v>
+      </c>
+      <c r="B83" t="s">
+        <v>16</v>
+      </c>
+      <c r="C83" t="n">
+        <v>-0.278736913784189</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>15</v>
+      </c>
+      <c r="B84" t="s">
+        <v>16</v>
+      </c>
+      <c r="C84" t="n">
+        <v>-0.00372294802059248</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>15</v>
+      </c>
+      <c r="B85" t="s">
+        <v>16</v>
+      </c>
+      <c r="C85" t="n">
+        <v>-0.706903512458943</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>15</v>
+      </c>
+      <c r="B86" t="s">
+        <v>16</v>
+      </c>
+      <c r="C86" t="n">
+        <v>-0.843880253069945</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>15</v>
+      </c>
+      <c r="B87" t="s">
+        <v>16</v>
+      </c>
+      <c r="C87" t="n">
+        <v>-0.813072156862386</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>15</v>
+      </c>
+      <c r="B88" t="s">
+        <v>16</v>
+      </c>
+      <c r="C88" t="n">
+        <v>-0.286941569908412</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>15</v>
+      </c>
+      <c r="B89" t="s">
+        <v>16</v>
+      </c>
+      <c r="C89" t="n">
+        <v>-0.59159409224596</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>15</v>
+      </c>
+      <c r="B90" t="s">
+        <v>16</v>
+      </c>
+      <c r="C90" t="n">
+        <v>-0.913873292574756</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>15</v>
+      </c>
+      <c r="B91" t="s">
+        <v>16</v>
+      </c>
+      <c r="C91" t="n">
+        <v>-0.941074655798136</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>15</v>
+      </c>
+      <c r="B92" t="s">
+        <v>16</v>
+      </c>
+      <c r="C92" t="n">
+        <v>-0.190377573552005</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>15</v>
+      </c>
+      <c r="B93" t="s">
+        <v>16</v>
+      </c>
+      <c r="C93" t="n">
+        <v>-3.20406576744967</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>15</v>
+      </c>
+      <c r="B94" t="s">
+        <v>16</v>
+      </c>
+      <c r="C94" t="n">
+        <v>-0.92309903262484</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>15</v>
+      </c>
+      <c r="B95" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0.302401495376153</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>15</v>
+      </c>
+      <c r="B96" t="s">
+        <v>16</v>
+      </c>
+      <c r="C96" t="n">
+        <v>-0.148328920922037</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>15</v>
+      </c>
+      <c r="B97" t="s">
+        <v>16</v>
+      </c>
+      <c r="C97" t="n">
+        <v>-0.832492766935923</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>15</v>
+      </c>
+      <c r="B98" t="s">
+        <v>16</v>
+      </c>
+      <c r="C98" t="n">
+        <v>-0.572635647414001</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>15</v>
+      </c>
+      <c r="B99" t="s">
+        <v>16</v>
+      </c>
+      <c r="C99" t="n">
+        <v>-0.180789652378234</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>15</v>
+      </c>
+      <c r="B100" t="s">
+        <v>16</v>
+      </c>
+      <c r="C100" t="n">
+        <v>0.401263514239771</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>15</v>
+      </c>
+      <c r="B101" t="s">
+        <v>16</v>
+      </c>
+      <c r="C101" t="n">
+        <v>-0.393696365001745</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>15</v>
+      </c>
+      <c r="B102" t="s">
+        <v>16</v>
+      </c>
+      <c r="C102" t="n">
+        <v>-0.824672475603362</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>15</v>
+      </c>
+      <c r="B103" t="s">
+        <v>16</v>
+      </c>
+      <c r="C103" t="n">
+        <v>0.45798808658264</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>15</v>
+      </c>
+      <c r="B104" t="s">
+        <v>16</v>
+      </c>
+      <c r="C104" t="n">
+        <v>-0.0786312762052606</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>15</v>
+      </c>
+      <c r="B105" t="s">
+        <v>16</v>
+      </c>
+      <c r="C105" t="n">
+        <v>-0.260240835962607</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>15</v>
+      </c>
+      <c r="B106" t="s">
+        <v>16</v>
+      </c>
+      <c r="C106" t="n">
+        <v>-0.293203042234903</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>15</v>
+      </c>
+      <c r="B107" t="s">
+        <v>16</v>
+      </c>
+      <c r="C107" t="n">
+        <v>-1.09144377529689</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>15</v>
+      </c>
+      <c r="B108" t="s">
+        <v>16</v>
+      </c>
+      <c r="C108" t="n">
+        <v>-0.497370133748948</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>15</v>
+      </c>
+      <c r="B109" t="s">
+        <v>16</v>
+      </c>
+      <c r="C109" t="n">
+        <v>0.194690057531753</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>15</v>
+      </c>
+      <c r="B110" t="s">
+        <v>16</v>
+      </c>
+      <c r="C110" t="n">
+        <v>0.246702817999207</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>15</v>
+      </c>
+      <c r="B111" t="s">
+        <v>16</v>
+      </c>
+      <c r="C111" t="n">
+        <v>-0.800243169287068</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>15</v>
+      </c>
+      <c r="B112" t="s">
+        <v>16</v>
+      </c>
+      <c r="C112" t="n">
+        <v>-0.20905011570801</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>15</v>
+      </c>
+      <c r="B113" t="s">
+        <v>16</v>
+      </c>
+      <c r="C113" t="n">
+        <v>-1.21388871528791</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>15</v>
+      </c>
+      <c r="B114" t="s">
+        <v>16</v>
+      </c>
+      <c r="C114" t="n">
+        <v>-0.974860794912505</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>15</v>
+      </c>
+      <c r="B115" t="s">
+        <v>16</v>
+      </c>
+      <c r="C115" t="n">
+        <v>-0.280940346114667</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>15</v>
+      </c>
+      <c r="B116" t="s">
+        <v>16</v>
+      </c>
+      <c r="C116" t="n">
+        <v>-1.95974240751005</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>15</v>
+      </c>
+      <c r="B117" t="s">
+        <v>16</v>
+      </c>
+      <c r="C117" t="n">
+        <v>-1.62708748359398</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>15</v>
+      </c>
+      <c r="B118" t="s">
+        <v>16</v>
+      </c>
+      <c r="C118" t="n">
+        <v>-0.40546252042178</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>15</v>
+      </c>
+      <c r="B119" t="s">
+        <v>16</v>
+      </c>
+      <c r="C119" t="n">
+        <v>-2.76403861731838</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>15</v>
+      </c>
+      <c r="B120" t="s">
+        <v>16</v>
+      </c>
+      <c r="C120" t="n">
+        <v>-0.925481170258807</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>15</v>
+      </c>
+      <c r="B121" t="s">
+        <v>16</v>
+      </c>
+      <c r="C121" t="n">
+        <v>-0.325732859745567</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>15</v>
+      </c>
+      <c r="B122" t="s">
+        <v>16</v>
+      </c>
+      <c r="C122" t="n">
+        <v>-0.547275031720049</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>15</v>
+      </c>
+      <c r="B123" t="s">
+        <v>16</v>
+      </c>
+      <c r="C123" t="n">
+        <v>-1.14125912085926</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>15</v>
+      </c>
+      <c r="B124" t="s">
+        <v>16</v>
+      </c>
+      <c r="C124" t="n">
+        <v>-0.233010266211569</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>15</v>
+      </c>
+      <c r="B125" t="s">
+        <v>16</v>
+      </c>
+      <c r="C125" t="n">
+        <v>-0.38069079999499</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>15</v>
+      </c>
+      <c r="B126" t="s">
+        <v>16</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.104564017878132</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>15</v>
+      </c>
+      <c r="B127" t="s">
+        <v>16</v>
+      </c>
+      <c r="C127" t="n">
+        <v>-0.260578817280939</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>15</v>
+      </c>
+      <c r="B128" t="s">
+        <v>16</v>
+      </c>
+      <c r="C128" t="n">
+        <v>-0.305027452131354</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>15</v>
+      </c>
+      <c r="B129" t="s">
+        <v>16</v>
+      </c>
+      <c r="C129" t="n">
+        <v>-0.613269079799221</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>15</v>
+      </c>
+      <c r="B130" t="s">
+        <v>16</v>
+      </c>
+      <c r="C130" t="n">
+        <v>-1.41098284501268</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>15</v>
+      </c>
+      <c r="B131" t="s">
+        <v>16</v>
+      </c>
+      <c r="C131" t="n">
+        <v>-1.02051617524248</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>15</v>
+      </c>
+      <c r="B132" t="s">
+        <v>16</v>
+      </c>
+      <c r="C132" t="n">
+        <v>-0.64369238439081</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>15</v>
+      </c>
+      <c r="B133" t="s">
+        <v>16</v>
+      </c>
+      <c r="C133" t="n">
+        <v>-0.526894821527744</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>15</v>
+      </c>
+      <c r="B134" t="s">
+        <v>16</v>
+      </c>
+      <c r="C134" t="n">
+        <v>-1.20787304281442</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>15</v>
+      </c>
+      <c r="B135" t="s">
+        <v>16</v>
+      </c>
+      <c r="C135" t="n">
+        <v>-1.08680388977436</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>15</v>
+      </c>
+      <c r="B136" t="s">
+        <v>16</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.0697815585608184</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>15</v>
+      </c>
+      <c r="B137" t="s">
+        <v>16</v>
+      </c>
+      <c r="C137" t="n">
+        <v>-0.123394802721238</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>15</v>
+      </c>
+      <c r="B138" t="s">
+        <v>16</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.1309320873525</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>15</v>
+      </c>
+      <c r="B139" t="s">
+        <v>16</v>
+      </c>
+      <c r="C139" t="n">
+        <v>-0.629538041487063</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>15</v>
+      </c>
+      <c r="B140" t="s">
+        <v>16</v>
+      </c>
+      <c r="C140" t="n">
+        <v>-0.768194865408893</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>15</v>
+      </c>
+      <c r="B141" t="s">
+        <v>16</v>
+      </c>
+      <c r="C141" t="n">
+        <v>-1.31552250973549</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>15</v>
+      </c>
+      <c r="B142" t="s">
+        <v>16</v>
+      </c>
+      <c r="C142" t="n">
+        <v>-0.825267244432255</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>15</v>
+      </c>
+      <c r="B143" t="s">
+        <v>16</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.0305074296584816</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>15</v>
+      </c>
+      <c r="B144" t="s">
+        <v>16</v>
+      </c>
+      <c r="C144" t="n">
+        <v>-0.80803372954338</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>15</v>
+      </c>
+      <c r="B145" t="s">
+        <v>16</v>
+      </c>
+      <c r="C145" t="n">
+        <v>-0.746511114313934</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>15</v>
+      </c>
+      <c r="B146" t="s">
+        <v>16</v>
+      </c>
+      <c r="C146" t="n">
+        <v>-0.832972917326466</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>15</v>
+      </c>
+      <c r="B147" t="s">
+        <v>16</v>
+      </c>
+      <c r="C147" t="n">
+        <v>-0.511945157699379</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>15</v>
+      </c>
+      <c r="B148" t="s">
+        <v>16</v>
+      </c>
+      <c r="C148" t="n">
+        <v>-1.13076881715662</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>15</v>
+      </c>
+      <c r="B149" t="s">
+        <v>16</v>
+      </c>
+      <c r="C149" t="n">
+        <v>-0.759733425139342</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>15</v>
+      </c>
+      <c r="B150" t="s">
+        <v>16</v>
+      </c>
+      <c r="C150" t="n">
+        <v>-0.0598154833650741</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>15</v>
+      </c>
+      <c r="B151" t="s">
+        <v>16</v>
+      </c>
+      <c r="C151" t="n">
+        <v>-0.518708229277108</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" t="s">
+        <v>16</v>
+      </c>
+      <c r="C152" t="n">
+        <v>-0.884975045678449</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>15</v>
+      </c>
+      <c r="B153" t="s">
+        <v>16</v>
+      </c>
+      <c r="C153" t="n">
+        <v>-0.618633307375576</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>15</v>
+      </c>
+      <c r="B154" t="s">
+        <v>16</v>
+      </c>
+      <c r="C154" t="n">
+        <v>-0.119932762662366</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>15</v>
+      </c>
+      <c r="B155" t="s">
+        <v>16</v>
+      </c>
+      <c r="C155" t="n">
+        <v>-1.56363341572646</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>15</v>
+      </c>
+      <c r="B156" t="s">
+        <v>16</v>
+      </c>
+      <c r="C156" t="n">
+        <v>-0.0290795198898555</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>15</v>
+      </c>
+      <c r="B157" t="s">
+        <v>16</v>
+      </c>
+      <c r="C157" t="n">
+        <v>-0.411516155496354</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>15</v>
+      </c>
+      <c r="B158" t="s">
+        <v>16</v>
+      </c>
+      <c r="C158" t="n">
+        <v>-0.550081932640978</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>15</v>
+      </c>
+      <c r="B159" t="s">
+        <v>16</v>
+      </c>
+      <c r="C159" t="n">
+        <v>-1.03761545585753</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>15</v>
+      </c>
+      <c r="B160" t="s">
+        <v>16</v>
+      </c>
+      <c r="C160" t="n">
+        <v>-0.416605746807406</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>15</v>
+      </c>
+      <c r="B161" t="s">
+        <v>16</v>
+      </c>
+      <c r="C161" t="n">
+        <v>-1.18928675826157</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>15</v>
+      </c>
+      <c r="B162" t="s">
+        <v>16</v>
+      </c>
+      <c r="C162" t="n">
+        <v>0.410356060748299</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>15</v>
+      </c>
+      <c r="B163" t="s">
+        <v>16</v>
+      </c>
+      <c r="C163" t="n">
+        <v>-0.153643274251979</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>15</v>
+      </c>
+      <c r="B164" t="s">
+        <v>16</v>
+      </c>
+      <c r="C164" t="n">
+        <v>-0.542933237926544</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>15</v>
+      </c>
+      <c r="B165" t="s">
+        <v>16</v>
+      </c>
+      <c r="C165" t="n">
+        <v>-0.230329821228117</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>15</v>
+      </c>
+      <c r="B166" t="s">
+        <v>16</v>
+      </c>
+      <c r="C166" t="n">
+        <v>0.0750548124460222</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>15</v>
+      </c>
+      <c r="B167" t="s">
+        <v>16</v>
+      </c>
+      <c r="C167" t="n">
+        <v>-1.10683822254868</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>15</v>
+      </c>
+      <c r="B168" t="s">
+        <v>16</v>
+      </c>
+      <c r="C168" t="n">
+        <v>-0.597942394587509</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>15</v>
+      </c>
+      <c r="B169" t="s">
+        <v>16</v>
+      </c>
+      <c r="C169" t="n">
+        <v>0.29257417362785</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>15</v>
+      </c>
+      <c r="B170" t="s">
+        <v>16</v>
+      </c>
+      <c r="C170" t="n">
+        <v>-0.502760419338802</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>15</v>
+      </c>
+      <c r="B171" t="s">
+        <v>16</v>
+      </c>
+      <c r="C171" t="n">
+        <v>-0.158747232702495</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>15</v>
+      </c>
+      <c r="B172" t="s">
+        <v>16</v>
+      </c>
+      <c r="C172" t="n">
+        <v>-1.62763921031956</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>15</v>
+      </c>
+      <c r="B173" t="s">
+        <v>16</v>
+      </c>
+      <c r="C173" t="n">
+        <v>-0.983666394927435</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>15</v>
+      </c>
+      <c r="B174" t="s">
+        <v>16</v>
+      </c>
+      <c r="C174" t="n">
+        <v>-1.37937531366573</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>15</v>
+      </c>
+      <c r="B175" t="s">
+        <v>16</v>
+      </c>
+      <c r="C175" t="n">
+        <v>-0.25270752081045</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>15</v>
+      </c>
+      <c r="B176" t="s">
+        <v>16</v>
+      </c>
+      <c r="C176" t="n">
+        <v>-0.642121479144206</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>15</v>
+      </c>
+      <c r="B177" t="s">
+        <v>16</v>
+      </c>
+      <c r="C177" t="n">
+        <v>-1.28957622181981</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>15</v>
+      </c>
+      <c r="B178" t="s">
+        <v>16</v>
+      </c>
+      <c r="C178" t="n">
+        <v>-0.166751446010349</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>15</v>
+      </c>
+      <c r="B179" t="s">
+        <v>16</v>
+      </c>
+      <c r="C179" t="n">
+        <v>-1.16881959391143</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>15</v>
+      </c>
+      <c r="B180" t="s">
+        <v>16</v>
+      </c>
+      <c r="C180" t="n">
+        <v>0.329721289874643</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>15</v>
+      </c>
+      <c r="B181" t="s">
+        <v>16</v>
+      </c>
+      <c r="C181" t="n">
+        <v>-0.577995899053852</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>15</v>
+      </c>
+      <c r="B182" t="s">
+        <v>16</v>
+      </c>
+      <c r="C182" t="n">
+        <v>-1.6576115756545</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>15</v>
+      </c>
+      <c r="B183" t="s">
+        <v>16</v>
+      </c>
+      <c r="C183" t="n">
+        <v>-0.971940903012738</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>15</v>
+      </c>
+      <c r="B184" t="s">
+        <v>16</v>
+      </c>
+      <c r="C184" t="n">
+        <v>-0.0187803466630574</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>15</v>
+      </c>
+      <c r="B185" t="s">
+        <v>16</v>
+      </c>
+      <c r="C185" t="n">
+        <v>-0.620410073873601</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>15</v>
+      </c>
+      <c r="B186" t="s">
+        <v>16</v>
+      </c>
+      <c r="C186" t="n">
+        <v>0.209036391163442</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>15</v>
+      </c>
+      <c r="B187" t="s">
+        <v>16</v>
+      </c>
+      <c r="C187" t="n">
+        <v>0.178093356372266</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>15</v>
+      </c>
+      <c r="B188" t="s">
+        <v>16</v>
+      </c>
+      <c r="C188" t="n">
+        <v>-0.0138419544642927</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>15</v>
+      </c>
+      <c r="B189" t="s">
+        <v>16</v>
+      </c>
+      <c r="C189" t="n">
+        <v>-0.175142658286337</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>15</v>
+      </c>
+      <c r="B190" t="s">
+        <v>16</v>
+      </c>
+      <c r="C190" t="n">
+        <v>-0.366966500698188</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>15</v>
+      </c>
+      <c r="B191" t="s">
+        <v>16</v>
+      </c>
+      <c r="C191" t="n">
+        <v>0.0309415771862644</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>15</v>
+      </c>
+      <c r="B192" t="s">
+        <v>16</v>
+      </c>
+      <c r="C192" t="n">
+        <v>-0.316820496945294</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>15</v>
+      </c>
+      <c r="B193" t="s">
+        <v>16</v>
+      </c>
+      <c r="C193" t="n">
+        <v>-0.720829053639277</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>15</v>
+      </c>
+      <c r="B194" t="s">
+        <v>16</v>
+      </c>
+      <c r="C194" t="n">
+        <v>-0.128552388993779</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>15</v>
+      </c>
+      <c r="B195" t="s">
+        <v>16</v>
+      </c>
+      <c r="C195" t="n">
+        <v>-0.214811445885812</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>15</v>
+      </c>
+      <c r="B196" t="s">
+        <v>16</v>
+      </c>
+      <c r="C196" t="n">
+        <v>-1.2885245045168</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>15</v>
+      </c>
+      <c r="B197" t="s">
+        <v>16</v>
+      </c>
+      <c r="C197" t="n">
+        <v>-0.440272845125618</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>15</v>
+      </c>
+      <c r="B198" t="s">
+        <v>16</v>
+      </c>
+      <c r="C198" t="n">
+        <v>-0.427145220038896</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>15</v>
+      </c>
+      <c r="B199" t="s">
+        <v>16</v>
+      </c>
+      <c r="C199" t="n">
+        <v>0.166937423938877</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>15</v>
+      </c>
+      <c r="B200" t="s">
+        <v>16</v>
+      </c>
+      <c r="C200" t="n">
+        <v>-0.102579398642405</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>15</v>
+      </c>
+      <c r="B201" t="s">
+        <v>16</v>
+      </c>
+      <c r="C201" t="n">
+        <v>-0.274076025854542</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
